--- a/data/dividends_info_20260906.xlsx
+++ b/data/dividends_info_20260906.xlsx
@@ -3311,7 +3311,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>ELSA Solutions S.p.A.</t>
+          <t>Gismondi 1754 S.p.A.</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -3345,7 +3345,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Gismondi 1754 S.p.A.</t>
+          <t>Giglio.com S.p.A.</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -3362,7 +3362,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Giglio.com S.p.A.</t>
+          <t>Intred S.p.A.</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -3379,7 +3379,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Intred S.p.A.</t>
+          <t>BRIOSCHI SVILUPPO IMMOBILIARE S.p.A</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -3447,7 +3447,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Egomnia S.p.A.</t>
+          <t>ELSA Solutions S.p.A.</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -3464,7 +3464,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>BRIOSCHI SVILUPPO IMMOBILIARE S.p.A</t>
+          <t>Egomnia S.p.A.</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -3481,7 +3481,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Cloudia Research S.p.A.</t>
+          <t>VINEXT S.p.A.</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -3498,7 +3498,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>DANIELI &amp; C. S.p.A.</t>
+          <t>gAIn360 S.p.A.</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -3508,14 +3508,14 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>FOPE S.p.A.</t>
+          <t>DANIELI &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -3525,14 +3525,14 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Ecomembrane S.p.A.</t>
+          <t>ESAUTOMOTION S.p.A.</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -3549,7 +3549,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>MIT SIM S.p.A.</t>
+          <t>Ecomembrane S.p.A.</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -3566,7 +3566,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Maps S.p.A.</t>
+          <t>FOPE S.p.A.</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -3583,7 +3583,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Pasquarelli Auto S.p.A.</t>
+          <t>ILPRA S.p.A.</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -3617,7 +3617,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>SBE-Varvit S.p.A.</t>
+          <t>Maps S.p.A.</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -3634,7 +3634,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>ESAUTOMOTION S.p.A.</t>
+          <t>Pasquarelli Auto S.p.A.</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -3651,7 +3651,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>BESTBE HOLDING S.p.A.</t>
+          <t>Svas Biosana S.p.A.</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -3668,7 +3668,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>ILPRA S.p.A.</t>
+          <t>SBE-Varvit S.p.A.</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -3719,7 +3719,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>SIAV S.p.A.</t>
+          <t>BESTBE HOLDING S.p.A.</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -3729,14 +3729,14 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Smart Capital S.p.A.</t>
+          <t>Cloudia Research S.p.A.</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -3753,7 +3753,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Svas Biosana S.p.A.</t>
+          <t>MIT SIM S.p.A.</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -3770,7 +3770,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>VINEXT S.p.A.</t>
+          <t>Smart Capital S.p.A.</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -3787,7 +3787,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>gAIn360 S.p.A.</t>
+          <t>SIAV S.p.A.</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -3797,14 +3797,14 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>PREMIA FINANCE S.P.A</t>
+          <t>Simone S.p.A.</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -3821,7 +3821,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>OMER S.p.A.</t>
+          <t>Edil San Felice S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -3831,7 +3831,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -3855,7 +3855,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>INNOVATEC S.p.A.</t>
+          <t>Edil San Felice S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -3872,7 +3872,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Longino &amp; Cardenal S.p.A.</t>
+          <t>T.P.S. S.p.A.</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -3889,7 +3889,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
+          <t>Energy S.p.A.</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -3906,7 +3906,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Radici Pietro Industries &amp; Brands S.p.A.</t>
+          <t>Estrima S.p.A.</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -3923,7 +3923,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>MARE ENGINEERING GROUP S.p.A.</t>
+          <t>INNOVATEC S.p.A.</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -3940,7 +3940,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>MARZOCCHI POMPE S.p.A.</t>
+          <t>EDILIZIACROBATICA S.p.A.</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -3950,14 +3950,14 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Markbass S.p.A.</t>
+          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -3974,7 +3974,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>FRENDY ENERGY S.p.A.</t>
+          <t>MARE ENGINEERING GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -3991,7 +3991,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Redelfi S.p.A.</t>
+          <t>MARZOCCHI POMPE S.p.A.</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -4008,7 +4008,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Tecno S.p.A. Società Benefit</t>
+          <t>Markbass S.p.A.</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -4025,7 +4025,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>T.P.S. S.p.A.</t>
+          <t>Metriks AI S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -4042,7 +4042,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>TMP Group S.p.A.</t>
+          <t>Next Geosolutions Europe S.p.A.</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -4059,7 +4059,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Telmes S.p.A.</t>
+          <t>Nusco S.p.A.</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -4076,7 +4076,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>TradeLab S.p.A.</t>
+          <t>Guidotti Ships S.p.A.</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -4093,7 +4093,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>CIRCLE S.p.A.</t>
+          <t>Longino &amp; Cardenal S.p.A.</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -4110,7 +4110,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>DBA GROUP S.p.A.</t>
+          <t>Farmacosmo S.p.A.</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -4127,7 +4127,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Estrima S.p.A.</t>
+          <t>Ambromobiliare S.p.A.</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -4144,7 +4144,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Energy S.p.A.</t>
+          <t>AEFFE S.p.A.</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -4154,14 +4154,14 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Edil San Felice S.p.A. Società Benefit</t>
+          <t>Redelfi S.p.A.</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -4178,7 +4178,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Edil San Felice S.p.A. Società Benefit</t>
+          <t>Radici Pietro Industries &amp; Brands S.p.A.</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -4188,14 +4188,14 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Metriks AI S.p.A. Società Benefit</t>
+          <t>PREMIA FINANCE S.P.A</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -4212,7 +4212,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>EDILIZIACROBATICA S.p.A.</t>
+          <t>OMER S.p.A.</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -4222,14 +4222,14 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Simone S.p.A.</t>
+          <t>CIRCLE S.p.A.</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -4246,7 +4246,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Next Geosolutions Europe S.p.A.</t>
+          <t>Triboo S.p.A.</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -4263,7 +4263,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Guidotti Ships S.p.A.</t>
+          <t>AEFFE S.p.A.</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -4273,14 +4273,14 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Triboo S.p.A.</t>
+          <t>YOLO GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -4297,7 +4297,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Farmacosmo S.p.A.</t>
+          <t>DBA GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -4314,7 +4314,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A.B.P. Nocivelli S.p.A.</t>
+          <t>TMP Group S.p.A.</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -4324,14 +4324,14 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A.B.P. Nocivelli S.p.A.</t>
+          <t>Tecno S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -4341,14 +4341,14 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>AEFFE S.p.A.</t>
+          <t>Telmes S.p.A.</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -4358,14 +4358,14 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Nusco S.p.A.</t>
+          <t>TradeLab S.p.A.</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -4382,7 +4382,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Ambromobiliare S.p.A.</t>
+          <t>A.B.P. Nocivelli S.p.A.</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -4392,14 +4392,14 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>ZEST S.p.A.</t>
+          <t>A.B.P. Nocivelli S.p.A.</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -4409,14 +4409,14 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>YOLO GROUP S.p.A.</t>
+          <t>ZEST S.p.A.</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -4433,7 +4433,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>AEFFE S.p.A.</t>
+          <t>FRENDY ENERGY S.p.A.</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -4443,14 +4443,14 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>PLANETEL S.p.A.</t>
+          <t>Vimi Fasteners S.p.A.</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -4467,7 +4467,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>International Care Company S.p.A.</t>
+          <t>Energy S.p.A.</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -4477,14 +4477,14 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Magis S.p.A.</t>
+          <t>Energy Time S.p.A.</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -4501,7 +4501,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Misitano &amp; Stracuzzi S.p.A.</t>
+          <t>EUKEDOS S.p.A.</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -4518,7 +4518,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Monnalisa S.p.A.</t>
+          <t>ETI S.p.A.</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -4535,7 +4535,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>NOTORIOUS PICTURES S.p.A.</t>
+          <t>EPH INVEST S.p.A.</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -4552,7 +4552,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Novamarine S.p.A.</t>
+          <t>FAE Technology Società Benefit S.p.A.</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -4569,7 +4569,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>OPS Italia S.p.A.</t>
+          <t>iVision Tech S.p.A.</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -4586,7 +4586,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Otofarma S.p.A.</t>
+          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -4596,14 +4596,14 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Lemon Sistemi S.p.A.</t>
+          <t>ErreDue S.p.A.</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -4620,7 +4620,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Reti S.p.A.</t>
+          <t>FIDIA S.p.A</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -4637,7 +4637,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>ISCC FINTECH S.p.A.</t>
+          <t>Distribuzione Elettrica Adriatica S.p.A.</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -4654,7 +4654,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>ATON Green Storage S.p.A.</t>
+          <t>Franchi Umberto Marmi S.p.A.</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -4671,7 +4671,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Adventure S.p.A.</t>
+          <t>UCapital24 S.p.A.</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -4688,7 +4688,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Alfio Bardolla Training Group S.p.A.</t>
+          <t>Reti S.p.A.</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -4705,7 +4705,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Arterra Bioscience S.p.A.</t>
+          <t>Racing Force S.p.A.</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -4722,7 +4722,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Bellini Nautica S.p.A.</t>
+          <t>PLANETEL S.p.A.</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -4739,7 +4739,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>COFLE S.p.A.</t>
+          <t>Otofarma S.p.A.</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -4756,7 +4756,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
+          <t>OPS Italia S.p.A.</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -4766,14 +4766,14 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>iVision Tech S.p.A.</t>
+          <t>Novamarine S.p.A.</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -4790,7 +4790,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>GEL S.p.A.</t>
+          <t>NOTORIOUS PICTURES S.p.A.</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -4807,7 +4807,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>GPI S.p.A.</t>
+          <t>Monnalisa S.p.A.</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -4824,7 +4824,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>GREEN OLEO S.p.A</t>
+          <t>First Capital S.p.A.</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -4841,7 +4841,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Gambero Rosso S.p.A.</t>
+          <t>Misitano &amp; Stracuzzi S.p.A.</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -4858,7 +4858,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Gens Aurea S.p.A.</t>
+          <t>ENA S.p.A.</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -4875,7 +4875,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Grifal S.p.A.</t>
+          <t>EDILIZIACROBATICA S.p.A.</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -4885,14 +4885,14 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>HIGH QUALITY FOOD S.p.A.</t>
+          <t>EDILIZIACROBATICA S.p.A.</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -4909,7 +4909,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Racing Force S.p.A.</t>
+          <t>E.T.S. S.p.A. Engineering and Technical Services</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -4926,7 +4926,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>BORGOSESIA S.p.A.</t>
+          <t>Datrix S.p.A.</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -4943,7 +4943,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>COMPAGNIA DEI CARAIBI S.p.A.</t>
+          <t>Copernico SIM S.p.A.</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -4960,7 +4960,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>First Capital S.p.A.</t>
+          <t>CSP INTERNATIONAL FASHION GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -4977,7 +4977,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>SOGES GROUP S.p.A.</t>
+          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -4994,7 +4994,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Saccheria F.lli Franceschetti S.p.A.</t>
+          <t>COMPAGNIA DEI CARAIBI S.p.A.</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -5011,7 +5011,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Seri Industrial S.p.A.</t>
+          <t>Magis S.p.A.</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -5028,7 +5028,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>ENA S.p.A.</t>
+          <t>Telesia S.p.A.</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -5045,7 +5045,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>EDILIZIACROBATICA S.p.A.</t>
+          <t>Bellini Nautica S.p.A.</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -5055,14 +5055,14 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>EDILIZIACROBATICA S.p.A.</t>
+          <t>Seri Industrial S.p.A.</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -5079,7 +5079,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>E.T.S. S.p.A. Engineering and Technical Services</t>
+          <t>COFLE S.p.A.</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -5096,7 +5096,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>Distribuzione Elettrica Adriatica S.p.A.</t>
+          <t>Riba Mundo Tecnologia S.A.</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -5113,7 +5113,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>Datrix S.p.A.</t>
+          <t>Lemon Sistemi S.p.A.</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -5130,7 +5130,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>Copernico SIM S.p.A.</t>
+          <t>International Care Company S.p.A.</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -5147,7 +5147,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>CSP INTERNATIONAL FASHION GROUP S.p.A.</t>
+          <t>ISCC FINTECH S.p.A.</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -5164,7 +5164,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
+          <t>HIGH QUALITY FOOD S.p.A.</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -5181,7 +5181,7 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>TESSELLIS S.p.A.</t>
+          <t>Grifal S.p.A.</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -5198,7 +5198,7 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>Telesia S.p.A.</t>
+          <t>Gens Aurea S.p.A.</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -5215,7 +5215,7 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>UCapital24 S.p.A.</t>
+          <t>Gambero Rosso S.p.A.</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -5232,7 +5232,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>Vimi Fasteners S.p.A.</t>
+          <t>GPI S.p.A.</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -5249,7 +5249,7 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>Franchi Umberto Marmi S.p.A.</t>
+          <t>GEL S.p.A.</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -5266,7 +5266,7 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>Rocket Sharing Company S.p.A.</t>
+          <t>GREEN OLEO S.p.A</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -5283,7 +5283,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>Riba Mundo Tecnologia S.A.</t>
+          <t>Adventure S.p.A.</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -5300,7 +5300,7 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>SOSTRAVEL.COM S.p.A.</t>
+          <t>TESSELLIS S.p.A.</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -5317,7 +5317,7 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>ETI S.p.A.</t>
+          <t>Alfio Bardolla Training Group S.p.A.</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -5334,7 +5334,7 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>Energy S.p.A.</t>
+          <t>Arterra Bioscience S.p.A.</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -5344,14 +5344,14 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>Energy Time S.p.A.</t>
+          <t>BORGOSESIA S.p.A.</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -5368,7 +5368,7 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>ErreDue S.p.A.</t>
+          <t>Rocket Sharing Company S.p.A.</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -5385,7 +5385,7 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>FAE Technology Società Benefit S.p.A.</t>
+          <t>SOGES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -5402,7 +5402,7 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>EPH INVEST S.p.A.</t>
+          <t>SOSTRAVEL.COM S.p.A.</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -5419,7 +5419,7 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>EUKEDOS S.p.A.</t>
+          <t>Saccheria F.lli Franceschetti S.p.A.</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -5436,7 +5436,7 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>FIDIA S.p.A</t>
+          <t>ATON Green Storage S.p.A.</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -5453,7 +5453,7 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>Dedem S.p.A.</t>
+          <t>PLC S.p.A.</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -5470,7 +5470,7 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>DESTINATION ITALIA S.p.A.</t>
+          <t>MEVIM S.p.A.</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -5487,7 +5487,7 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>E-Globe S.p.A.</t>
+          <t>Portobello S.p.A.</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -5504,7 +5504,7 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>ECOSUNTEK S.p.A.</t>
+          <t>Piu' Medical S.p.A.</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -5521,7 +5521,7 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>ESPE S.p.A.</t>
+          <t>PROMOTICA S.p.A.</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -5538,7 +5538,7 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>DEODATO.GALLERY S.p.A.</t>
+          <t>Officina Stellare S.p.A.</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -5555,7 +5555,7 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>Cube Labs S.p.A.</t>
+          <t>Met.Extra Group S.p.A.</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -5572,7 +5572,7 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>Com.Tel S.p.A.</t>
+          <t>OPS ECOM S.p.A.</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -5582,14 +5582,14 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>Cogefeed S.p.A.</t>
+          <t>Lucisano Media Group S.p.A.</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -5606,7 +5606,7 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>Dipietro Group S.p.A.</t>
+          <t>Litix S.p.A.</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -5623,7 +5623,7 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>VNE S.p.A.</t>
+          <t>Leone Film Group S.p.A.</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -5640,7 +5640,7 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
+          <t>KALEON S.P.A.</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -5657,7 +5657,7 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>The Italian Sea Group S.p.A.</t>
+          <t>Itway S.p.A.</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -5667,14 +5667,14 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>Tenax International S.p.A.</t>
+          <t>IDNTT S.A.</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -5691,7 +5691,7 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>TRAWELL CO S.p.A.</t>
+          <t>HELYX INDUSTRIES S.p.A.</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -5708,7 +5708,7 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>Vantea Smart S.p.A.</t>
+          <t>Gentili Mosconi S.p.A.</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -5725,7 +5725,7 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>Vivenda Group S.p.A.</t>
+          <t>Cogefeed S.p.A.</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -5742,7 +5742,7 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>doxee S.p.A.</t>
+          <t>OPT S.p.A.</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -5759,7 +5759,7 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>Valica S.p.A.</t>
+          <t>Com.Tel S.p.A.</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -5776,7 +5776,7 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>MONDO TV S.p.A.</t>
+          <t>DEODATO.GALLERY S.p.A.</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -5793,7 +5793,7 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>Praexidia Industrie Strategiche S.p.A.</t>
+          <t>DESTINATION ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -5810,7 +5810,7 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>ROSETTI MARINO S.p.A.</t>
+          <t>Dedem S.p.A.</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -5827,7 +5827,7 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>Racing Force S.p.A.</t>
+          <t>Dipietro Group S.p.A.</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -5837,14 +5837,14 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>RedFish LongTerm Capital S.p.A.</t>
+          <t>E-Globe S.p.A.</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -5861,7 +5861,7 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>Renovalo S.p.A.</t>
+          <t>ECOSUNTEK S.p.A.</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -5878,7 +5878,7 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>Reway Group S.p.A.</t>
+          <t>ESPE S.p.A.</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -5895,7 +5895,7 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>Pozzi Milano S.p.A.</t>
+          <t>MONDO TV S.p.A.</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -5929,7 +5929,7 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>Portobello S.p.A.</t>
+          <t>Cube Labs S.p.A.</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -5946,7 +5946,7 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>OPS ECOM S.p.A.</t>
+          <t>TRAWELL CO S.p.A.</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -5956,14 +5956,14 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>Met.Extra Group S.p.A.</t>
+          <t>doxee S.p.A.</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -5980,7 +5980,7 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>Litix S.p.A.</t>
+          <t>The Italian Sea Group S.p.A.</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -5990,14 +5990,14 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>Lucisano Media Group S.p.A.</t>
+          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -6014,7 +6014,7 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>MEVIM S.p.A.</t>
+          <t>Reway Group S.p.A.</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -6031,7 +6031,7 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>MONDO TV FRANCE</t>
+          <t>Renovalo S.p.A.</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -6048,7 +6048,7 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>G.M. Leather S.p.A.</t>
+          <t>RedFish LongTerm Capital S.p.A.</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -6065,7 +6065,7 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>First Point S.p.A.</t>
+          <t>Racing Force S.p.A.</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -6075,14 +6075,14 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>Finanza.tech S.p.A. Società Benefit</t>
+          <t>ROSETTI MARINO S.p.A.</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -6099,7 +6099,7 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>FRANCHETTI S.p.A.</t>
+          <t>Praexidia Industrie Strategiche S.p.A.</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -6116,7 +6116,7 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>Execus S.p.A.</t>
+          <t>Società Editoriale il Fatto S.p.A.</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -6133,7 +6133,7 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>Eprcomunicazione S.p.A. Società Benefit</t>
+          <t>Pozzi Milano S.p.A.</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -6150,7 +6150,7 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>Energy Time S.p.A.</t>
+          <t>Casta Diva Group S.p.A.</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -6160,14 +6160,14 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>Emma Villas S.p.A.</t>
+          <t>CLASS EDITORI S.p.A.</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -6184,7 +6184,7 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>EdgeLab S.p.A.</t>
+          <t>B.F. S.p.A.</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -6201,7 +6201,7 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>EXPERT.AI S.p.A.</t>
+          <t>Alia Mentis S.p.A.</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -6218,7 +6218,7 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>KALEON S.P.A.</t>
+          <t>ACQUAZZURRA S.p.A.</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -6235,7 +6235,7 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>Itway S.p.A.</t>
+          <t>ABC Company S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -6252,7 +6252,7 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>Leone Film Group S.p.A.</t>
+          <t>AATECH S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -6269,7 +6269,7 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>HELYX INDUSTRIES S.p.A.</t>
+          <t>CleanBnB S.p.A.</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -6286,7 +6286,7 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>OPT S.p.A.</t>
+          <t>Tenax International S.p.A.</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -6303,7 +6303,7 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>Officina Stellare S.p.A.</t>
+          <t>Solid World Group S.p.A.</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -6320,7 +6320,7 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>PLC S.p.A.</t>
+          <t>EdgeLab S.p.A.</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -6337,7 +6337,7 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>PROMOTICA S.p.A.</t>
+          <t>VNE S.p.A.</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -6354,7 +6354,7 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>Piu' Medical S.p.A.</t>
+          <t>Valica S.p.A.</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -6371,7 +6371,7 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>CleanBnB S.p.A.</t>
+          <t>Vantea Smart S.p.A.</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -6388,7 +6388,7 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>Casta Diva Group S.p.A.</t>
+          <t>Vivenda Group S.p.A.</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -6405,7 +6405,7 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>CLASS EDITORI S.p.A.</t>
+          <t>EXPERT.AI S.p.A.</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -6422,7 +6422,7 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>IDNTT S.A.</t>
+          <t>Emma Villas S.p.A.</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -6439,7 +6439,7 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>Solid World Group S.p.A.</t>
+          <t>MONDO TV FRANCE</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -6456,7 +6456,7 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>Alia Mentis S.p.A.</t>
+          <t>Eprcomunicazione S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -6473,7 +6473,7 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>ACQUAZZURRA S.p.A.</t>
+          <t>Execus S.p.A.</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -6490,7 +6490,7 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>ABC Company S.p.A. Società Benefit</t>
+          <t>FRANCHETTI S.p.A.</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -6507,7 +6507,7 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>AATECH S.p.A. Società Benefit</t>
+          <t>Finanza.tech S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -6524,7 +6524,7 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>Società Editoriale il Fatto S.p.A.</t>
+          <t>First Point S.p.A.</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -6541,7 +6541,7 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>Gentili Mosconi S.p.A.</t>
+          <t>G.M. Leather S.p.A.</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -6558,7 +6558,7 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>B.F. S.p.A.</t>
+          <t>Energy Time S.p.A.</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -6568,14 +6568,14 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>Renovalo S.p.A.</t>
+          <t>S.S. Lazio S.p.A.</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -6585,14 +6585,14 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>SB Annual Report</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>S.S. Lazio S.p.A.</t>
+          <t>Renovalo S.p.A.</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -6602,7 +6602,7 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>SB Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
